--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.75756</v>
+        <v>16.76362</v>
       </c>
       <c r="D2" t="n">
-        <v>16.50555</v>
+        <v>16.34449</v>
       </c>
       <c r="E2" t="n">
-        <v>16.53352</v>
+        <v>16.52134</v>
       </c>
       <c r="F2" t="n">
-        <v>42.32027</v>
+        <v>41.80555</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04924</v>
+        <v>0.05004</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83306</v>
+        <v>1.84565</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.92456</v>
+        <v>16.60798</v>
       </c>
       <c r="D3" t="n">
-        <v>16.65953</v>
+        <v>16.42004</v>
       </c>
       <c r="E3" t="n">
-        <v>16.26455</v>
+        <v>16.4336</v>
       </c>
       <c r="F3" t="n">
-        <v>42.17869</v>
+        <v>42.3761</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05008</v>
+        <v>0.05001</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7935</v>
+        <v>1.76967</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.65485</v>
+        <v>16.57155</v>
       </c>
       <c r="D4" t="n">
-        <v>16.41903</v>
+        <v>16.30385</v>
       </c>
       <c r="E4" t="n">
-        <v>16.57449</v>
+        <v>16.44488</v>
       </c>
       <c r="F4" t="n">
-        <v>42.27816</v>
+        <v>41.5183</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05026</v>
+        <v>0.04996</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83879</v>
+        <v>1.79969</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.46407</v>
+        <v>16.60002</v>
       </c>
       <c r="D5" t="n">
-        <v>16.46763</v>
+        <v>16.25305</v>
       </c>
       <c r="E5" t="n">
-        <v>16.63803</v>
+        <v>16.30257</v>
       </c>
       <c r="F5" t="n">
-        <v>41.708</v>
+        <v>43.2602</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05057</v>
+        <v>0.04969</v>
       </c>
       <c r="H5" t="n">
-        <v>1.79332</v>
+        <v>1.8541</v>
       </c>
     </row>
     <row r="6">
@@ -559,10 +559,23 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>scratched - not measurable</t>
-        </is>
+      <c r="C6" t="n">
+        <v>16.93443</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16.5327</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16.57678</v>
+      </c>
+      <c r="F6" t="n">
+        <v>42.39867</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.05014</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.81932</v>
       </c>
     </row>
     <row r="7">
@@ -572,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.64476</v>
+        <v>16.99241</v>
       </c>
       <c r="D7" t="n">
-        <v>16.24225</v>
+        <v>16.66231</v>
       </c>
       <c r="E7" t="n">
-        <v>16.69793</v>
+        <v>16.69147</v>
       </c>
       <c r="F7" t="n">
-        <v>41.70965</v>
+        <v>43.09754</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05003</v>
+        <v>0.05027</v>
       </c>
       <c r="H7" t="n">
-        <v>1.84595</v>
+        <v>1.80606</v>
       </c>
     </row>
     <row r="8">
@@ -597,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.53788</v>
+        <v>17.09165</v>
       </c>
       <c r="D8" t="n">
-        <v>16.61148</v>
+        <v>16.44467</v>
       </c>
       <c r="E8" t="n">
-        <v>16.40445</v>
+        <v>17.03028</v>
       </c>
       <c r="F8" t="n">
-        <v>42.38146</v>
+        <v>41.41227</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05152</v>
+        <v>0.05147</v>
       </c>
       <c r="H8" t="n">
-        <v>1.80665</v>
+        <v>1.7716</v>
       </c>
     </row>
     <row r="9">
@@ -622,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.73508</v>
+        <v>16.82319</v>
       </c>
       <c r="D9" t="n">
-        <v>16.70604</v>
+        <v>16.44885</v>
       </c>
       <c r="E9" t="n">
-        <v>16.18495</v>
+        <v>16.76201</v>
       </c>
       <c r="F9" t="n">
-        <v>42.47266</v>
+        <v>42.47991</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05008</v>
+        <v>0.04979</v>
       </c>
       <c r="H9" t="n">
-        <v>1.80254</v>
+        <v>1.81193</v>
       </c>
     </row>
     <row r="10">
@@ -647,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.31421</v>
+        <v>16.54944</v>
       </c>
       <c r="D10" t="n">
-        <v>16.19217</v>
+        <v>16.48928</v>
       </c>
       <c r="E10" t="n">
-        <v>16.19641</v>
+        <v>16.51827</v>
       </c>
       <c r="F10" t="n">
-        <v>42.55136</v>
+        <v>42.25452</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0504</v>
+        <v>0.05</v>
       </c>
       <c r="H10" t="n">
-        <v>1.83393</v>
+        <v>1.79313</v>
       </c>
     </row>
     <row r="11">
@@ -703,21 +716,6 @@
           <t>Trace 1</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>16.6134</v>
-      </c>
-      <c r="D12" t="n">
-        <v>15.85621</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.3429</v>
-      </c>
-      <c r="F12" t="n">
-        <v>21.66129</v>
-      </c>
-      <c r="G12" t="n">
-        <v>34.52577</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -725,21 +723,6 @@
           <t>Unit 8</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>17.29605</v>
-      </c>
-      <c r="D13" t="n">
-        <v>15.73591</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.40262</v>
-      </c>
-      <c r="F13" t="n">
-        <v>22.29939</v>
-      </c>
-      <c r="G13" t="n">
-        <v>33.91555</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -747,26 +730,6 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>re-measured</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>16.99756</v>
-      </c>
-      <c r="D14" t="n">
-        <v>16.07947</v>
-      </c>
-      <c r="E14" t="n">
-        <v>16.33134</v>
-      </c>
-      <c r="F14" t="n">
-        <v>21.7498</v>
-      </c>
-      <c r="G14" t="n">
-        <v>34.69095</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -774,21 +737,6 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>16.78855</v>
-      </c>
-      <c r="D15" t="n">
-        <v>16.04494</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.10124</v>
-      </c>
-      <c r="F15" t="n">
-        <v>21.82039</v>
-      </c>
-      <c r="G15" t="n">
-        <v>33.57786</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -796,21 +744,6 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>16.35489</v>
-      </c>
-      <c r="D16" t="n">
-        <v>15.9886</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.61786</v>
-      </c>
-      <c r="F16" t="n">
-        <v>21.57722</v>
-      </c>
-      <c r="G16" t="n">
-        <v>34.4973</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -818,21 +751,6 @@
           <t>Unit 6</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>16.74078</v>
-      </c>
-      <c r="D17" t="n">
-        <v>15.5848</v>
-      </c>
-      <c r="E17" t="n">
-        <v>15.7996</v>
-      </c>
-      <c r="F17" t="n">
-        <v>21.54558</v>
-      </c>
-      <c r="G17" t="n">
-        <v>33.38791</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -840,21 +758,6 @@
           <t>Unit 1</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>16.7533</v>
-      </c>
-      <c r="D18" t="n">
-        <v>15.65886</v>
-      </c>
-      <c r="E18" t="n">
-        <v>16.4496</v>
-      </c>
-      <c r="F18" t="n">
-        <v>21.55537</v>
-      </c>
-      <c r="G18" t="n">
-        <v>34.07728</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -862,21 +765,6 @@
           <t>Unit 2</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>16.52059</v>
-      </c>
-      <c r="D19" t="n">
-        <v>15.76911</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.10715</v>
-      </c>
-      <c r="F19" t="n">
-        <v>21.91259</v>
-      </c>
-      <c r="G19" t="n">
-        <v>34.50607</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -884,21 +772,6 @@
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>16.56081</v>
-      </c>
-      <c r="D20" t="n">
-        <v>15.78275</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.17457</v>
-      </c>
-      <c r="F20" t="n">
-        <v>21.7442</v>
-      </c>
-      <c r="G20" t="n">
-        <v>33.70122</v>
-      </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
@@ -954,28 +827,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.74926</v>
+        <v>0.74105</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0813</v>
+        <v>0.08049000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.60498</v>
+        <v>0.6033500000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.94515</v>
+        <v>0.97204</v>
       </c>
       <c r="G22" t="n">
-        <v>0.10697</v>
+        <v>0.1074</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00744</v>
+        <v>0.00758</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09097</v>
+        <v>0.09306</v>
       </c>
       <c r="J22" t="n">
-        <v>0.12726</v>
+        <v>0.12623</v>
       </c>
     </row>
     <row r="23">
@@ -985,28 +858,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.74733</v>
+        <v>0.74483</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08004</v>
+        <v>0.07994</v>
       </c>
       <c r="E23" t="n">
-        <v>0.60412</v>
+        <v>0.60503</v>
       </c>
       <c r="F23" t="n">
-        <v>0.94913</v>
+        <v>0.9561500000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>0.10903</v>
+        <v>0.10926</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0076</v>
+        <v>0.00744</v>
       </c>
       <c r="I23" t="n">
-        <v>0.09055000000000001</v>
+        <v>0.09296</v>
       </c>
       <c r="J23" t="n">
-        <v>0.12484</v>
+        <v>0.12444</v>
       </c>
     </row>
     <row r="24">
@@ -1016,28 +889,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.74474</v>
+        <v>0.74125</v>
       </c>
       <c r="D24" t="n">
-        <v>0.07935</v>
+        <v>0.07998</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.60505</v>
       </c>
       <c r="F24" t="n">
-        <v>0.94934</v>
+        <v>0.96383</v>
       </c>
       <c r="G24" t="n">
-        <v>0.10964</v>
+        <v>0.10757</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0078</v>
+        <v>0.00755</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09317</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.12495</v>
+        <v>0.12621</v>
       </c>
     </row>
     <row r="25">
@@ -1047,28 +920,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.75801</v>
+        <v>0.75137</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08083</v>
+        <v>0.07889</v>
       </c>
       <c r="E25" t="n">
-        <v>0.60238</v>
+        <v>0.61553</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9417</v>
+        <v>0.94641</v>
       </c>
       <c r="G25" t="n">
-        <v>0.10849</v>
+        <v>0.10741</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0074</v>
+        <v>0.00738</v>
       </c>
       <c r="I25" t="n">
-        <v>0.09154</v>
+        <v>0.09277000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>0.12537</v>
+        <v>0.12527</v>
       </c>
     </row>
     <row r="26">
@@ -1078,28 +951,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.75187</v>
+        <v>0.75865</v>
       </c>
       <c r="D26" t="n">
-        <v>0.07998</v>
+        <v>0.08101</v>
       </c>
       <c r="E26" t="n">
-        <v>0.60494</v>
+        <v>0.59765</v>
       </c>
       <c r="F26" t="n">
-        <v>0.97066</v>
+        <v>0.97684</v>
       </c>
       <c r="G26" t="n">
-        <v>0.10815</v>
+        <v>0.1101</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0076</v>
+        <v>0.00762</v>
       </c>
       <c r="I26" t="n">
-        <v>0.08912</v>
+        <v>0.09329</v>
       </c>
       <c r="J26" t="n">
-        <v>0.12561</v>
+        <v>0.12684</v>
       </c>
     </row>
     <row r="27">
@@ -1109,28 +982,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.75475</v>
+        <v>0.74641</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08073</v>
+        <v>0.08061</v>
       </c>
       <c r="E27" t="n">
-        <v>0.59823</v>
+        <v>0.60229</v>
       </c>
       <c r="F27" t="n">
-        <v>0.94029</v>
+        <v>0.92914</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1077</v>
+        <v>0.10778</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00751</v>
+        <v>0.00753</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09182999999999999</v>
+        <v>0.09253</v>
       </c>
       <c r="J27" t="n">
-        <v>0.12561</v>
+        <v>0.12385</v>
       </c>
     </row>
     <row r="28">
@@ -1140,28 +1013,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.737</v>
+        <v>0.75227</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08125</v>
+        <v>0.08061</v>
       </c>
       <c r="E28" t="n">
-        <v>0.59294</v>
+        <v>0.59835</v>
       </c>
       <c r="F28" t="n">
-        <v>0.95627</v>
+        <v>0.96112</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1076</v>
+        <v>0.10801</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00774</v>
+        <v>0.0075</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09306</v>
+        <v>0.09325</v>
       </c>
       <c r="J28" t="n">
-        <v>0.12453</v>
+        <v>0.12598</v>
       </c>
     </row>
     <row r="29">
@@ -1171,28 +1044,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.74517</v>
+        <v>0.73339</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.08057</v>
       </c>
       <c r="E29" t="n">
-        <v>0.59926</v>
+        <v>0.60795</v>
       </c>
       <c r="F29" t="n">
-        <v>0.95413</v>
+        <v>0.95573</v>
       </c>
       <c r="G29" t="n">
-        <v>0.10835</v>
+        <v>0.10833</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00764</v>
+        <v>0.00765</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09261999999999999</v>
+        <v>0.09243999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>0.12556</v>
+        <v>0.12522</v>
       </c>
     </row>
     <row r="30">
@@ -1202,28 +1075,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.75243</v>
+        <v>0.75257</v>
       </c>
       <c r="D30" t="n">
-        <v>0.07957</v>
+        <v>0.07951</v>
       </c>
       <c r="E30" t="n">
-        <v>0.60615</v>
+        <v>0.60575</v>
       </c>
       <c r="F30" t="n">
-        <v>0.94414</v>
+        <v>0.93998</v>
       </c>
       <c r="G30" t="n">
-        <v>0.10754</v>
+        <v>0.10853</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00746</v>
+        <v>0.00768</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09132</v>
+        <v>0.09557</v>
       </c>
       <c r="J30" t="n">
-        <v>0.12451</v>
+        <v>0.12304</v>
       </c>
     </row>
   </sheetData>
